--- a/artfynd/A 56289-2025 artfynd.xlsx
+++ b/artfynd/A 56289-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136125709</v>
       </c>
       <c r="B2" t="n">
-        <v>89468</v>
+        <v>89470</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>136122024</v>
       </c>
       <c r="B3" t="n">
-        <v>92373</v>
+        <v>92376</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>136122033</v>
       </c>
       <c r="B4" t="n">
-        <v>92373</v>
+        <v>92376</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>136122017</v>
       </c>
       <c r="B6" t="n">
-        <v>92102</v>
+        <v>92105</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>136122023</v>
       </c>
       <c r="B7" t="n">
-        <v>92102</v>
+        <v>92105</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>136122029</v>
       </c>
       <c r="B8" t="n">
-        <v>92102</v>
+        <v>92105</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>136122014</v>
       </c>
       <c r="B9" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>136122013</v>
       </c>
       <c r="B10" t="n">
-        <v>92065</v>
+        <v>92068</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>136122022</v>
       </c>
       <c r="B11" t="n">
-        <v>92065</v>
+        <v>92068</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>136122032</v>
       </c>
       <c r="B12" t="n">
-        <v>92065</v>
+        <v>92068</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>136125713</v>
       </c>
       <c r="B13" t="n">
-        <v>92065</v>
+        <v>92068</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>136122025</v>
       </c>
       <c r="B49" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         <v>136125720</v>
       </c>
       <c r="B50" t="n">
-        <v>98204</v>
+        <v>98207</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 56289-2025 artfynd.xlsx
+++ b/artfynd/A 56289-2025 artfynd.xlsx
@@ -819,7 +819,7 @@
         <v>136122024</v>
       </c>
       <c r="B3" t="n">
-        <v>92376</v>
+        <v>92377</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>136122033</v>
       </c>
       <c r="B4" t="n">
-        <v>92376</v>
+        <v>92377</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>136122017</v>
       </c>
       <c r="B6" t="n">
-        <v>92105</v>
+        <v>92106</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>136122023</v>
       </c>
       <c r="B7" t="n">
-        <v>92105</v>
+        <v>92106</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>136122029</v>
       </c>
       <c r="B8" t="n">
-        <v>92105</v>
+        <v>92106</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>136122014</v>
       </c>
       <c r="B9" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>136122013</v>
       </c>
       <c r="B10" t="n">
-        <v>92068</v>
+        <v>92069</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>136122022</v>
       </c>
       <c r="B11" t="n">
-        <v>92068</v>
+        <v>92069</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>136122032</v>
       </c>
       <c r="B12" t="n">
-        <v>92068</v>
+        <v>92069</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>136125713</v>
       </c>
       <c r="B13" t="n">
-        <v>92068</v>
+        <v>92069</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>136122025</v>
       </c>
       <c r="B49" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         <v>136125720</v>
       </c>
       <c r="B50" t="n">
-        <v>98207</v>
+        <v>98208</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 56289-2025 artfynd.xlsx
+++ b/artfynd/A 56289-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136125709</v>
       </c>
       <c r="B2" t="n">
-        <v>89470</v>
+        <v>89472</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>136122024</v>
       </c>
       <c r="B3" t="n">
-        <v>92377</v>
+        <v>92382</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>136122033</v>
       </c>
       <c r="B4" t="n">
-        <v>92377</v>
+        <v>92382</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>136122017</v>
       </c>
       <c r="B6" t="n">
-        <v>92106</v>
+        <v>92111</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>136122023</v>
       </c>
       <c r="B7" t="n">
-        <v>92106</v>
+        <v>92111</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>136122029</v>
       </c>
       <c r="B8" t="n">
-        <v>92106</v>
+        <v>92111</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>136122014</v>
       </c>
       <c r="B9" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>136122013</v>
       </c>
       <c r="B10" t="n">
-        <v>92069</v>
+        <v>92074</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>136122022</v>
       </c>
       <c r="B11" t="n">
-        <v>92069</v>
+        <v>92074</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>136122032</v>
       </c>
       <c r="B12" t="n">
-        <v>92069</v>
+        <v>92074</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>136125713</v>
       </c>
       <c r="B13" t="n">
-        <v>92069</v>
+        <v>92074</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>136122006</v>
       </c>
       <c r="B14" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>136122009</v>
       </c>
       <c r="B15" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>136122010</v>
       </c>
       <c r="B16" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         <v>136122012</v>
       </c>
       <c r="B17" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>136122016</v>
       </c>
       <c r="B18" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>136122019</v>
       </c>
       <c r="B19" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         <v>136122026</v>
       </c>
       <c r="B20" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>136122027</v>
       </c>
       <c r="B21" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>136122028</v>
       </c>
       <c r="B22" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>136122031</v>
       </c>
       <c r="B23" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>136125702</v>
       </c>
       <c r="B24" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3509,7 +3509,7 @@
         <v>136125703</v>
       </c>
       <c r="B25" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
         <v>136125704</v>
       </c>
       <c r="B26" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         <v>136125705</v>
       </c>
       <c r="B27" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>136125706</v>
       </c>
       <c r="B28" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4033,7 +4033,7 @@
         <v>136125710</v>
       </c>
       <c r="B29" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4164,7 +4164,7 @@
         <v>136125714</v>
       </c>
       <c r="B30" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         <v>136125716</v>
       </c>
       <c r="B31" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>136125719</v>
       </c>
       <c r="B32" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4557,7 +4557,7 @@
         <v>136125721</v>
       </c>
       <c r="B33" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         <v>136122007</v>
       </c>
       <c r="B34" t="n">
-        <v>79498</v>
+        <v>79500</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         <v>136122015</v>
       </c>
       <c r="B35" t="n">
-        <v>79498</v>
+        <v>79500</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4912,7 +4912,7 @@
         <v>136122011</v>
       </c>
       <c r="B36" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
         <v>136122020</v>
       </c>
       <c r="B38" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5246,7 +5246,7 @@
         <v>136125712</v>
       </c>
       <c r="B39" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5473,7 +5473,7 @@
         <v>136122034</v>
       </c>
       <c r="B41" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>136122030</v>
       </c>
       <c r="B42" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5718,7 +5718,7 @@
         <v>136125707</v>
       </c>
       <c r="B43" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v>136125715</v>
       </c>
       <c r="B44" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
         <v>136140095</v>
       </c>
       <c r="B45" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6078,7 +6078,7 @@
         <v>136122018</v>
       </c>
       <c r="B46" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6206,7 +6206,7 @@
         <v>136122008</v>
       </c>
       <c r="B47" t="n">
-        <v>58162</v>
+        <v>58164</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6334,7 +6334,7 @@
         <v>136122021</v>
       </c>
       <c r="B48" t="n">
-        <v>56570</v>
+        <v>56572</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>136122025</v>
       </c>
       <c r="B49" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         <v>136125720</v>
       </c>
       <c r="B50" t="n">
-        <v>98208</v>
+        <v>98213</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
         <v>136125718</v>
       </c>
       <c r="B51" t="n">
-        <v>79158</v>
+        <v>79160</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6803,7 +6803,7 @@
         <v>136140093</v>
       </c>
       <c r="B52" t="n">
-        <v>79158</v>
+        <v>79160</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
